--- a/Q4/对照汇总.xlsx
+++ b/Q4/对照汇总.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总体结果" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="反事实分解" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="风险指标" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="成本结构" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="约束活跃率与灵活性" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总体结果" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反事实分解" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险指标" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本结构" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="约束活跃率与灵活性" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1397.36242</v>
+        <v>1397.36025</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>186.542134</v>
+        <v>186.514561</v>
       </c>
       <c r="E2" t="n">
-        <v>1583.904553</v>
+        <v>1583.874811</v>
       </c>
       <c r="F2" t="n">
-        <v>477.719198</v>
+        <v>477.630276</v>
       </c>
       <c r="G2" t="n">
         <v>655.891692</v>
       </c>
       <c r="H2" t="n">
-        <v>8.915615000000001</v>
+        <v>8.91564</v>
       </c>
       <c r="I2" t="n">
-        <v>47422.292018</v>
+        <v>47421.401523</v>
       </c>
       <c r="J2" t="n">
         <v>0.61872</v>
@@ -543,10 +543,10 @@
         <v>12593.120478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.897084</v>
+        <v>0.897089</v>
       </c>
       <c r="M2" t="n">
-        <v>3.904849</v>
+        <v>3.904999</v>
       </c>
     </row>
     <row r="3">
@@ -556,28 +556,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1453.366171</v>
+        <v>1453.375424</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>196.771908</v>
+        <v>196.774613</v>
       </c>
       <c r="E3" t="n">
-        <v>1650.138079</v>
+        <v>1650.150038</v>
       </c>
       <c r="F3" t="n">
-        <v>475.261118</v>
+        <v>475.27251</v>
       </c>
       <c r="G3" t="n">
         <v>681.0155</v>
       </c>
       <c r="H3" t="n">
-        <v>9.630603000000001</v>
+        <v>9.63076</v>
       </c>
       <c r="I3" t="n">
-        <v>49405.331711</v>
+        <v>49405.68975</v>
       </c>
       <c r="J3" t="n">
         <v>0.641904</v>
@@ -586,10 +586,10 @@
         <v>13075.497609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.899508</v>
+        <v>0.8995069999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>4.14029</v>
+        <v>4.140248</v>
       </c>
     </row>
     <row r="4">
@@ -602,37 +602,37 @@
         <v>1231.094198</v>
       </c>
       <c r="C4" t="n">
-        <v>57.538316</v>
+        <v>57.279516</v>
       </c>
       <c r="D4" t="n">
-        <v>122.995987</v>
+        <v>123.37341</v>
       </c>
       <c r="E4" t="n">
-        <v>1411.628501</v>
+        <v>1411.747125</v>
       </c>
       <c r="F4" t="n">
-        <v>278.285879</v>
+        <v>279.292636</v>
       </c>
       <c r="G4" t="n">
-        <v>646.428452</v>
+        <v>646.359137</v>
       </c>
       <c r="H4" t="n">
-        <v>6.309247</v>
+        <v>6.309403</v>
       </c>
       <c r="I4" t="n">
-        <v>42264.326391</v>
+        <v>42267.878006</v>
       </c>
       <c r="J4" t="n">
-        <v>0.604981</v>
+        <v>0.604979</v>
       </c>
       <c r="K4" t="n">
-        <v>12411.426279</v>
+        <v>12410.095422</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9192669999999999</v>
+        <v>0.919369</v>
       </c>
       <c r="M4" t="n">
-        <v>4.419771</v>
+        <v>4.417353</v>
       </c>
     </row>
     <row r="5">
@@ -645,37 +645,37 @@
         <v>1289.542727</v>
       </c>
       <c r="C5" t="n">
-        <v>60.97458</v>
+        <v>61.120827</v>
       </c>
       <c r="D5" t="n">
-        <v>123.775001</v>
+        <v>123.25156</v>
       </c>
       <c r="E5" t="n">
-        <v>1474.292309</v>
+        <v>1473.915115</v>
       </c>
       <c r="F5" t="n">
-        <v>280.149142</v>
+        <v>278.8434</v>
       </c>
       <c r="G5" t="n">
-        <v>674.327794</v>
+        <v>674.626339</v>
       </c>
       <c r="H5" t="n">
-        <v>7.423946</v>
+        <v>7.425968</v>
       </c>
       <c r="I5" t="n">
-        <v>44140.488281</v>
+        <v>44129.195065</v>
       </c>
       <c r="J5" t="n">
-        <v>0.63222</v>
+        <v>0.632228</v>
       </c>
       <c r="K5" t="n">
-        <v>12947.093652</v>
+        <v>12952.825715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.919676</v>
+        <v>0.919669</v>
       </c>
       <c r="M5" t="n">
-        <v>4.418182</v>
+        <v>4.4201</v>
       </c>
     </row>
   </sheetData>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15839045.534</v>
+        <v>15838748.1088</v>
       </c>
       <c r="C2" t="n">
-        <v>14116285.0146</v>
+        <v>14117471.254</v>
       </c>
     </row>
     <row r="3">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16641525.1034</v>
+        <v>16641452.9592</v>
       </c>
       <c r="C3" t="n">
-        <v>14872447.1715</v>
+        <v>14873198.1439</v>
       </c>
     </row>
     <row r="4">
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16501380.7914</v>
+        <v>16501500.3765</v>
       </c>
       <c r="C4" t="n">
-        <v>14742923.0859</v>
+        <v>14739151.1516</v>
       </c>
     </row>
     <row r="5">
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>802479.5693</v>
+        <v>802704.8504</v>
       </c>
       <c r="C5" t="n">
-        <v>756162.1568</v>
+        <v>755726.89</v>
       </c>
     </row>
     <row r="6">
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-140144.312</v>
+        <v>-139952.5827</v>
       </c>
       <c r="C6" t="n">
-        <v>-129524.0855</v>
+        <v>-134046.9923</v>
       </c>
     </row>
   </sheetData>
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47422.292018</v>
+        <v>47421.401523</v>
       </c>
       <c r="C2" t="n">
-        <v>49405.331711</v>
+        <v>49405.68975</v>
       </c>
       <c r="D2" t="n">
-        <v>42264.326391</v>
+        <v>42267.878006</v>
       </c>
       <c r="E2" t="n">
-        <v>44140.488281</v>
+        <v>44129.195065</v>
       </c>
     </row>
     <row r="3">
@@ -856,10 +856,10 @@
         <v>49236.351546</v>
       </c>
       <c r="C3" t="n">
-        <v>49914.041512</v>
+        <v>49919.51274</v>
       </c>
       <c r="D3" t="n">
-        <v>45927.707111</v>
+        <v>45868.045022</v>
       </c>
       <c r="E3" t="n">
         <v>46572.079133</v>
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18263.952231</v>
+        <v>18265.398079</v>
       </c>
       <c r="C4" t="n">
-        <v>22516.435392</v>
+        <v>22517.221778</v>
       </c>
       <c r="D4" t="n">
-        <v>14021.558347</v>
+        <v>14014.988404</v>
       </c>
       <c r="E4" t="n">
-        <v>18500.286438</v>
+        <v>18504.067806</v>
       </c>
     </row>
     <row r="5">
@@ -900,7 +900,7 @@
         <v>15643.852442</v>
       </c>
       <c r="E5" t="n">
-        <v>11767.745505</v>
+        <v>11721.956959</v>
       </c>
     </row>
     <row r="6">
@@ -935,7 +935,7 @@
         <v>76970.442201</v>
       </c>
       <c r="D7" t="n">
-        <v>57663.320692</v>
+        <v>57640.049364</v>
       </c>
       <c r="E7" t="n">
         <v>66019.068828</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70764.81426299999</v>
+        <v>70739.342732</v>
       </c>
       <c r="C8" t="n">
         <v>80299.270237</v>
@@ -957,7 +957,7 @@
         <v>61992.110184</v>
       </c>
       <c r="E8" t="n">
-        <v>72452.929275</v>
+        <v>72387.413696</v>
       </c>
     </row>
     <row r="9">
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78914.08255000001</v>
+        <v>78914.210733</v>
       </c>
       <c r="C9" t="n">
-        <v>87422.60599500001</v>
+        <v>87423.389923</v>
       </c>
       <c r="D9" t="n">
-        <v>61455.696468</v>
+        <v>61419.416845</v>
       </c>
       <c r="E9" t="n">
-        <v>71652.174933</v>
+        <v>71686.02196699999</v>
       </c>
     </row>
     <row r="10">
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89156.14771999999</v>
+        <v>89156.404087</v>
       </c>
       <c r="C10" t="n">
-        <v>96306.02768100001</v>
+        <v>96307.59553799999</v>
       </c>
       <c r="D10" t="n">
-        <v>63092.466739</v>
+        <v>63094.033878</v>
       </c>
       <c r="E10" t="n">
-        <v>74239.458489</v>
+        <v>74259.67674</v>
       </c>
     </row>
     <row r="11">
@@ -1008,13 +1008,13 @@
         <v>119033.019229</v>
       </c>
       <c r="C11" t="n">
-        <v>124634.774093</v>
+        <v>124641.34136</v>
       </c>
       <c r="D11" t="n">
-        <v>64179.69517</v>
+        <v>64240.488717</v>
       </c>
       <c r="E11" t="n">
-        <v>75817.571945</v>
+        <v>75936.579962</v>
       </c>
     </row>
     <row r="12">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.063787</v>
+        <v>0.063794</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06399100000000001</v>
+        <v>0.06399199999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.045045</v>
+        <v>0.045041</v>
       </c>
       <c r="E12" t="n">
-        <v>0.050872</v>
+        <v>0.050922</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.874686</v>
+        <v>0.87491</v>
       </c>
       <c r="C3" t="n">
-        <v>0.041359</v>
+        <v>0.041468</v>
       </c>
       <c r="D3" t="n">
-        <v>0.083956</v>
+        <v>0.083622</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1195,10 +1195,10 @@
         <v>0.142735</v>
       </c>
       <c r="D2" t="n">
-        <v>0.11974</v>
+        <v>0.119615</v>
       </c>
       <c r="E2" t="n">
-        <v>0.126081</v>
+        <v>0.125956</v>
       </c>
     </row>
     <row r="3">
@@ -1217,7 +1217,7 @@
         <v>0.015116</v>
       </c>
       <c r="E3" t="n">
-        <v>0.015095</v>
+        <v>0.014887</v>
       </c>
     </row>
     <row r="4">
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05383</v>
+        <v>0.053892</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07019300000000001</v>
+        <v>0.069964</v>
       </c>
       <c r="D4" t="n">
-        <v>0.101381</v>
+        <v>0.09990400000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.108159</v>
+        <v>0.109864</v>
       </c>
     </row>
     <row r="5">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.137787</v>
+        <v>0.137413</v>
       </c>
       <c r="C5" t="n">
-        <v>0.153027</v>
+        <v>0.152653</v>
       </c>
       <c r="D5" t="n">
-        <v>0.069715</v>
+        <v>0.069964</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07416399999999999</v>
+        <v>0.07445499999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1271,10 +1271,10 @@
         <v>0.560585</v>
       </c>
       <c r="D6" t="n">
-        <v>0.610779</v>
+        <v>0.610778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.565284</v>
+        <v>0.565335</v>
       </c>
     </row>
     <row r="7">
@@ -1290,10 +1290,10 @@
         <v>681.0155</v>
       </c>
       <c r="D7" t="n">
-        <v>646.428452</v>
+        <v>646.359137</v>
       </c>
       <c r="E7" t="n">
-        <v>674.327794</v>
+        <v>674.626339</v>
       </c>
     </row>
     <row r="8">
@@ -1309,10 +1309,10 @@
         <v>544.8124</v>
       </c>
       <c r="D8" t="n">
-        <v>517.1427619999999</v>
+        <v>517.087309</v>
       </c>
       <c r="E8" t="n">
-        <v>539.462236</v>
+        <v>539.701071</v>
       </c>
     </row>
     <row r="9">
@@ -1322,16 +1322,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.897084</v>
+        <v>0.897089</v>
       </c>
       <c r="C9" t="n">
-        <v>0.899508</v>
+        <v>0.8995069999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9192669999999999</v>
+        <v>0.919369</v>
       </c>
       <c r="E9" t="n">
-        <v>0.919676</v>
+        <v>0.919669</v>
       </c>
     </row>
     <row r="10">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.051502</v>
+        <v>0.051511</v>
       </c>
       <c r="C10" t="n">
-        <v>0.043796</v>
+        <v>0.043795</v>
       </c>
       <c r="D10" t="n">
         <v>0.000126</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04343</v>
+        <v>0.043552</v>
       </c>
     </row>
     <row r="11">
@@ -1366,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>589836.181879</v>
+        <v>587068.90418</v>
       </c>
       <c r="E11" t="n">
-        <v>591401.012118</v>
+        <v>592663.7335870001</v>
       </c>
     </row>
     <row r="12">
